--- a/database/seeders/excel/device.xlsx
+++ b/database/seeders/excel/device.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F27EE85-4202-464E-91DD-7D6C630F7599}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F722432-48DF-4408-98EC-FDD43C4464AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/database/seeders/excel/device.xlsx
+++ b/database/seeders/excel/device.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F722432-48DF-4408-98EC-FDD43C4464AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C9B1ED-F927-4084-8ED9-608624BC3B9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="1034">
   <si>
     <t>id</t>
   </si>
@@ -3118,6 +3118,15 @@
   </si>
   <si>
     <t>id_user</t>
+  </si>
+  <si>
+    <t>3060201004-1</t>
+  </si>
+  <si>
+    <t>Realme</t>
+  </si>
+  <si>
+    <t>Realme Note 50</t>
   </si>
 </sst>
 </file>
@@ -3435,7 +3444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K512"/>
+  <dimension ref="A1:K513"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -8798,7 +8807,7 @@
         <v>294</v>
       </c>
       <c r="K153">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -21349,6 +21358,41 @@
       </c>
       <c r="K512">
         <v>340014249</v>
+      </c>
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B513">
+        <v>8</v>
+      </c>
+      <c r="C513">
+        <v>2025</v>
+      </c>
+      <c r="D513">
+        <v>2</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F513" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G513" t="s">
+        <v>6</v>
+      </c>
+      <c r="H513">
+        <v>1</v>
+      </c>
+      <c r="I513">
+        <v>1</v>
+      </c>
+      <c r="J513" t="s">
+        <v>6</v>
+      </c>
+      <c r="K513">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
